--- a/informed_consent_forms/020_high_frequency_skin_treatment_consent_form--informed_consent_forms.xlsx
+++ b/informed_consent_forms/020_high_frequency_skin_treatment_consent_form--informed_consent_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -853,8 +853,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="31" customWidth="1" min="2" max="2"/>
+    <col width="31" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -882,12 +882,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'normal_skin'}</t>
+          <t>normal_skin</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Normal Skin'}</t>
+          <t>Normal Skin</t>
         </is>
       </c>
     </row>
@@ -899,12 +899,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'sensitive_skin'}</t>
+          <t>sensitive_skin</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Sensitive Skin'}</t>
+          <t>Sensitive Skin</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'rosacea_skin'}</t>
+          <t>rosacea_skin</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Rosacea Skin'}</t>
+          <t>Rosacea Skin</t>
         </is>
       </c>
     </row>
@@ -933,12 +933,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'once_a_month'}</t>
+          <t>once_a_month</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Once a month'}</t>
+          <t>Once a month</t>
         </is>
       </c>
     </row>
@@ -950,12 +950,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'twice_a_month'}</t>
+          <t>twice_a_month</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Twice a month'}</t>
+          <t>Twice a month</t>
         </is>
       </c>
     </row>
@@ -967,12 +967,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'weekly'}</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Weekly'}</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
@@ -984,12 +984,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'daily'}</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Daily'}</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
@@ -1001,12 +1001,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'initial_consultation'}</t>
+          <t>initial_consultation</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Initial Consultation'}</t>
+          <t>Initial Consultation</t>
         </is>
       </c>
     </row>
@@ -1018,12 +1018,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'initial_and_future_treatments'}</t>
+          <t>initial_and_future_treatments</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Initial and Future Treatments'}</t>
+          <t>Initial and Future Treatments</t>
         </is>
       </c>
     </row>
